--- a/src/attributions/attributions_ig_traj_315.xlsx
+++ b/src/attributions/attributions_ig_traj_315.xlsx
@@ -1568,19 +1568,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.02418872420424001</v>
+        <v>-0.04094582715906889</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2200313556820915</v>
+        <v>0.04984062268341264</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0297222616785872</v>
+        <v>0.006008104106640712</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1589,16 +1589,16 @@
         <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.04549870858509959</v>
+        <v>-0.03381648685467318</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1669696547688765</v>
+        <v>0.08508756658317751</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,67 +1607,67 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.08793382720306485</v>
+        <v>-0.019488891209108</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03002647149756665</v>
+        <v>0.03608303428629883</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2759595619679406</v>
+        <v>0.03250596167179787</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2259773188101408</v>
+        <v>-0.002160052523204211</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1293565113266864</v>
+        <v>0.02966148043584454</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1887597180749193</v>
+        <v>0.01530638937479216</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.02200606635111935</v>
+        <v>-0.03708440172169628</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>-0</v>
@@ -1676,133 +1676,133 @@
         <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.04241004905476619</v>
+        <v>0.02050450933768893</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1193690168140054</v>
+        <v>0.04460744684037452</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1046518276625959</v>
+        <v>0.04828624270874199</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.06674363746653625</v>
+        <v>-0.04380453227371123</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.4580023110862685</v>
+        <v>0.1976285498331249</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.3460235442622456</v>
+        <v>-0.05145822003143298</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.02138687793230071</v>
+        <v>-0.03337101898750801</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.00143794356464338</v>
+        <v>-0.02771320275793164</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.2259338143168571</v>
+        <v>-0.02256923077622319</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.005730755690935645</v>
+        <v>0.02782067663976412</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1354406829429332</v>
+        <v>0.06017552907239344</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.04789229746031805</v>
+        <v>0.05108238412269079</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.03653895399165603</v>
+        <v>0.0005758233457988497</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.2270015904255228</v>
+        <v>0.1284553829711113</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1073967884823989</v>
+        <v>0.02460682086685028</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
@@ -1811,25 +1811,25 @@
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.003724299811516963</v>
+        <v>0.02476249473009557</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.1531130309075819</v>
+        <v>-0.05752334372632883</v>
       </c>
       <c r="CF3" t="n">
         <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.01628814487349426</v>
+        <v>-0.02211230138977833</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
@@ -1838,52 +1838,52 @@
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.05871014575969947</v>
+        <v>-0.02171416213728048</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01359439955521128</v>
+        <v>-0.05851144849859168</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.06282621355883128</v>
+        <v>-0.02523956069945584</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
         <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.005476650159356101</v>
+        <v>0.007254995160553438</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.1617260153526258</v>
+        <v>-0.06084269293048019</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.04408565746745696</v>
+        <v>-0.04567747416634779</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,19 +1892,19 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.01055219681941233</v>
+        <v>-0.002957886977201465</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.16563546743433</v>
+        <v>-0.09670189040868322</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.17240437128512</v>
+        <v>-0.01564373647189595</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
@@ -1919,19 +1919,19 @@
         <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.008757020276307276</v>
+        <v>-0.001802148959140245</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.08265679328352746</v>
+        <v>-0.02062023106792351</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.03289190760824105</v>
+        <v>-0.0530847516220013</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1940,43 +1940,43 @@
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.04845833783252517</v>
+        <v>0.0120866637888087</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.2099038051855881</v>
+        <v>-0.08364789500858258</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0155969365992562</v>
+        <v>-0.03074169497620063</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.01106968010325099</v>
+        <v>0.0174320048184524</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.01538031735356012</v>
+        <v>0.003833868659291382</v>
       </c>
       <c r="EH3" t="n">
         <v>-0</v>
@@ -1985,79 +1985,79 @@
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0345416073012147</v>
+        <v>-0.04629890175367163</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.00374746304716561</v>
+        <v>-0.0003544228998180693</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.1592610955208959</v>
+        <v>-0.03324461643616836</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.07064251265362115</v>
+        <v>-0.008620244699926909</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.04599662591196098</v>
+        <v>0.0141874402750532</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.1747045504942426</v>
+        <v>-0.09034768863328184</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.0458613042130303</v>
+        <v>-0.04119790410983017</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.02584844386790417</v>
+        <v>0.03957840114819647</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.002901016692310751</v>
+        <v>0.05075501895087683</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
@@ -2066,10 +2066,10 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.04615485745654523</v>
+        <v>-0.008903999634275324</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2081,55 +2081,55 @@
         <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.00280688665697219</v>
+        <v>0.06356505577090965</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.139830419950609</v>
+        <v>-0.00304736867164489</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.04678404558843365</v>
+        <v>0.08189018539847738</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.08631778359305563</v>
+        <v>0.06297795513544081</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.06437603949026414</v>
+        <v>-0.03826811988823541</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -2709,151 +2709,151 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3821494470478233</v>
+        <v>0.2742702149540569</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09035592151531911</v>
+        <v>-0.124403083101757</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0116952463271177</v>
+        <v>-0.06511330618663376</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2683722874397212</v>
+        <v>0.2523652256460132</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1427083011313939</v>
+        <v>-0.2208054384427562</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.04067111131023712</v>
+        <v>-0.1144772370222257</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2259355155225513</v>
+        <v>0.1432517348353673</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01472072358672192</v>
+        <v>-0.01187760370236355</v>
       </c>
       <c r="W5" t="n">
-        <v>0.101651994267757</v>
+        <v>-0.03378378290889846</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1643609679411407</v>
+        <v>-0.07567808349766533</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.05284613333842066</v>
+        <v>-0.2189605542912227</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.05265678415218668</v>
+        <v>-0.0894024190739378</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.04455406785344213</v>
+        <v>0.179929283153414</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.1060252106004767</v>
+        <v>-0.06359731031726551</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.09655003789164714</v>
+        <v>0.08120099048875375</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.6202811552199051</v>
+        <v>0.4627613009322061</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001530211197834593</v>
+        <v>-0.2331730939254659</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.3200170293287111</v>
+        <v>-0.3427781088346958</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -2868,106 +2868,106 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.09048391718706543</v>
+        <v>0.07557467971449272</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1400462121027152</v>
+        <v>-0.1244304544485455</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1583404909250349</v>
+        <v>-0.01197820275497997</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.09599766630002636</v>
+        <v>-0.003782337109419154</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.736237930658723e-10</v>
+        <v>1.011336298433973e-10</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.2672212705710151</v>
+        <v>0.05647143125839747</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2856645645870545</v>
+        <v>0.3644650554942203</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.006513710775406804</v>
+        <v>-0.1267252609989379</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1010475262813417</v>
+        <v>-0.06404410147929433</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1828712824539747</v>
+        <v>-0.1682736708274945</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.008513721609256987</v>
+        <v>0.1807482700518462</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.03904653798347287</v>
+        <v>0.01002091748034531</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2979,49 +2979,49 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.003520200603787978</v>
+        <v>-0.1225082277318083</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.07477835585415893</v>
+        <v>0.09967644024396152</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.08887459198342182</v>
+        <v>0.02899835193769162</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1704977416518282</v>
+        <v>-0.1783818487448472</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.05476525978655281</v>
+        <v>0.1917554132756239</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.04037683805656317</v>
+        <v>0.02251336538896172</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
@@ -3033,16 +3033,16 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1125181931824674</v>
+        <v>-0.1875798129176154</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.02772851044987139</v>
+        <v>0.2120958495208273</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.1404050412087204</v>
+        <v>0.01461353061347637</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
@@ -3051,112 +3051,112 @@
         <v>-0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.05140230347928419</v>
+        <v>-0.07921630606752578</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.1897597337943069</v>
+        <v>0.04965432192362439</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.05073473130033784</v>
+        <v>0.053450148414818</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.1105192949330235</v>
+        <v>0.019330199184332</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.01516169621503362</v>
+        <v>0.1449326787944168</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.04971503835073981</v>
+        <v>-0.05254101185467682</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1200874788926249</v>
+        <v>-0.1348379189591998</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.03764571437829783</v>
+        <v>0.158781249522981</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.07621592994308599</v>
+        <v>0.01021833773666411</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1570880257210974</v>
+        <v>-0.1648572854020008</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.1584502302892646</v>
+        <v>-0.1113987921039682</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.1409284632056253</v>
+        <v>-0.0552629542617717</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.177975622826188</v>
+        <v>-0.2043487099713279</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.008748908913090105</v>
+        <v>0.2104515599156157</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.03367501607677309</v>
+        <v>-0.006781934579463428</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
@@ -3195,16 +3195,16 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01492019278253352</v>
+        <v>-0.1113880594550113</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.07687831274953436</v>
+        <v>0.08438277796796301</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.008695540359522903</v>
+        <v>-0.03768536344182603</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3213,61 +3213,61 @@
         <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01043175891341315</v>
+        <v>-0.06123200657495848</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.09627839589419901</v>
+        <v>0.2424385984638154</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.02831212637375988</v>
+        <v>0.3235821313475977</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.02023786868060947</v>
+        <v>-0.1429299453290704</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.09054083964495947</v>
+        <v>0.06423430895484472</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,19 +3275,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.06313585016943975</v>
+        <v>-0.01438493819440789</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1882671564130776</v>
+        <v>0.05258980493635391</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02745135346174129</v>
+        <v>-0.009874731536166722</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3296,16 +3296,16 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.04843479297889542</v>
+        <v>-0.01032756328128125</v>
       </c>
       <c r="K6" t="n">
-        <v>0.15614344849081</v>
+        <v>0.06460027026076989</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.06429800145659099</v>
+        <v>-0.01908016187677424</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3329,52 +3329,52 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02435814504362715</v>
+        <v>0.009342530420902367</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2401318604861579</v>
+        <v>0.01121833936626533</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1739682732895886</v>
+        <v>-0.003864146827149411</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1067115591262039</v>
+        <v>-0.006107014591268206</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2268543711748027</v>
+        <v>-0.001773311899349107</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.00621643986201883</v>
+        <v>-0.001486887251018105</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
@@ -3383,37 +3383,37 @@
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.01860613356464509</v>
+        <v>-0.003654678143412588</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1247734253951045</v>
+        <v>0.03126588057582809</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.09682125813116901</v>
+        <v>0.01717216523782078</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.05458105365862774</v>
+        <v>-0.01221629249466668</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.351814601104987</v>
+        <v>0.07975276280355267</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,25 +3422,25 @@
         <v>-0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.3403486416287762</v>
+        <v>-0.02545168529848613</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.05267495364774184</v>
+        <v>-0.01435103348334889</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.07459079090065077</v>
+        <v>0.01253507654932651</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.2161174039819752</v>
+        <v>-0.01263956083869768</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,10 +3464,10 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.05219732612316347</v>
+        <v>-0.007705937800396344</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.1368547787035415</v>
+        <v>-0.007530043751232087</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,13 +3476,13 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.03407779139571914</v>
+        <v>0.02923749782798165</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3491,103 +3491,103 @@
         <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0449875606692293</v>
+        <v>0.004227223687190144</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2252535220797068</v>
+        <v>0.05469626592198259</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1278876465219609</v>
+        <v>-0.005021944396437927</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.01708897173721447</v>
+        <v>0.01121034529534669</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.09395137490425655</v>
+        <v>-0.035390491758637</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.00827574357103201</v>
+        <v>0.003342754258709688</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
         <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.03643795264472406</v>
+        <v>0.0002609355422840038</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.01271395128251974</v>
+        <v>-0.02605223198281494</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.08228858538015241</v>
+        <v>0.006358358298297621</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0008688762166999901</v>
+        <v>0.006558181423377497</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.0998328754112741</v>
+        <v>-0.03490731034180642</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.01382936356622434</v>
+        <v>0.002846975253527833</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB6" t="n">
         <v>0</v>
@@ -3599,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0008780792123925787</v>
+        <v>-0.004105635774092601</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.2035680838782173</v>
+        <v>-0.03733425181383609</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
@@ -3611,25 +3611,25 @@
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07739026555400975</v>
+        <v>-0.005179167232923406</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM6" t="n">
         <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.001904205912134952</v>
+        <v>0.004536341645769285</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.04470699689480248</v>
+        <v>-0.0244691602235422</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
@@ -3638,7 +3638,7 @@
         <v>-0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.03444127262079089</v>
+        <v>0.002557522174906526</v>
       </c>
       <c r="DS6" t="n">
         <v>-0</v>
@@ -3647,16 +3647,16 @@
         <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.003950987971657648</v>
+        <v>0.01794208486755181</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.1153654482840355</v>
+        <v>0.02167015292749548</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,25 +3665,25 @@
         <v>0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01324980438114479</v>
+        <v>0.0009165881550230754</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.0248620962105348</v>
+        <v>0.002631316734728895</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.01053074602692411</v>
+        <v>-0.02345823394567587</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.009296834733056581</v>
+        <v>-0.01104801981452812</v>
       </c>
       <c r="EK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
@@ -3707,52 +3707,52 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>-0.0294515127238547</v>
+        <v>0.002237712817645119</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.1224521184582286</v>
+        <v>-0.01523408873199471</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.007516735200477506</v>
+        <v>-0.001116594814631998</v>
       </c>
       <c r="ET6" t="n">
         <v>-0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.002671072534930568</v>
+        <v>0.01000132933526987</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1106757970771266</v>
+        <v>-0.03940249254545135</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.05772977325522639</v>
+        <v>-0.0009962691988218665</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,10 +3761,10 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0391234600895399</v>
+        <v>-0.002371205828337828</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.02859375630662538</v>
+        <v>-0.01637308936741471</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,7 +3773,7 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.09581574419480209</v>
+        <v>0.009595647396275745</v>
       </c>
       <c r="FL6" t="n">
         <v>0</v>
@@ -3788,10 +3788,10 @@
         <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>-0.0006133646333114966</v>
+        <v>0.03956243278414653</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.1833632910510785</v>
+        <v>-0.01745101930505507</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,28 +3800,28 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.1587525917319661</v>
+        <v>0.008276474082456345</v>
       </c>
       <c r="FU6" t="n">
         <v>-0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0.06941182898395502</v>
+        <v>0.01861188041192002</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02316097726990948</v>
+        <v>-0.02550891611320964</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3839,7 +3839,7 @@
         <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,16 +3847,16 @@
         <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4189996827936351</v>
+        <v>0.512462326976092</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2108741035800564</v>
+        <v>-0.3162322466496855</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08116204226821093</v>
+        <v>-0.1532299939087526</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3107948646360413</v>
+        <v>0.4439249297586368</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2019241198607944</v>
+        <v>-0.4583230049698434</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1173760225682975</v>
+        <v>-0.2371774677654614</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1506699438613633</v>
+        <v>0.2165144816851489</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01472805785408143</v>
+        <v>-0.01933513694251835</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06499697987717597</v>
+        <v>-0.007590930212344883</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -3928,22 +3928,22 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1052546472003839</v>
+        <v>0.04313942403642356</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.01168694256061556</v>
+        <v>-0.1570773467585974</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.05876040983814525</v>
+        <v>0.02044645665597371</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3952,73 +3952,73 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.09063679243962698</v>
+        <v>0.3108519527987941</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1052450769722249</v>
+        <v>-0.02990318412604844</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.05467919992740666</v>
+        <v>0.2744635169967815</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.729532663338716</v>
+        <v>0.8932706134710512</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.09650676496266747</v>
+        <v>-0.4180757048027368</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1419101424891255</v>
+        <v>-0.2723775329968164</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0118755824620538</v>
+        <v>-0.0624768957464534</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1110358859651311</v>
+        <v>-0.05297318839194074</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.2015211491027306</v>
+        <v>-0.1006384658130871</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,34 +4027,34 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.01470809071633556</v>
+        <v>-0.1091211662945409</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1102853389158</v>
+        <v>0.006536378770090977</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.06536640436113419</v>
+        <v>0.1427610874460158</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
         <v>-0</v>
@@ -4063,43 +4063,43 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.3427259711285105</v>
+        <v>0.5556447833658427</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.03144160096055756</v>
+        <v>-0.2729808222291876</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.05064675697588566</v>
+        <v>-0.06967148758547995</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1410015443655865</v>
+        <v>-0.3132913307699955</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0799952590632704</v>
+        <v>0.1925394097386604</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.04349526657048009</v>
+        <v>0.04613500451315496</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.003177014996402034</v>
+        <v>-0.2049345743138949</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.05420093627591995</v>
+        <v>0.08319427041489437</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1277234642604479</v>
+        <v>0.04279152987386205</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,49 +4138,49 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1349694924494129</v>
+        <v>-0.3402597806316883</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.1108093884749646</v>
+        <v>0.2052177230956551</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.03458531664680947</v>
+        <v>0.07653066023898171</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1247052690052953</v>
+        <v>-0.4458344938961234</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1751026480473944</v>
+        <v>0.2949151244583046</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.1672132542952342</v>
+        <v>-0.1232663687755622</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,7 +4189,7 @@
         <v>-0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
         <v>0</v>
@@ -4198,19 +4198,19 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.07423479511749602</v>
+        <v>-0.08086251858476186</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.005083053557561757</v>
+        <v>0.1380639511237208</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.05369995649940546</v>
+        <v>-0.1233820303258594</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,25 +4225,25 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.04732621844579117</v>
+        <v>0.1862820062042294</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.03373602634553284</v>
+        <v>0.1299997227274327</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.007743932200983096</v>
+        <v>-0.0549638563171902</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
@@ -4252,16 +4252,16 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1413046949586716</v>
+        <v>-0.2427345139701719</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.08613947329070139</v>
+        <v>0.1567876404326094</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.1303304469290352</v>
+        <v>0.1091186102169643</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
@@ -4270,7 +4270,7 @@
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,22 +4279,22 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.08702650649662934</v>
+        <v>-0.3007541735208658</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.1545855629742793</v>
+        <v>0.1339809373530413</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.1408272579874814</v>
+        <v>0.02319734017798804</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,100 +4306,100 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1447031321554928</v>
+        <v>-0.3722234020220476</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.1103337322664111</v>
+        <v>0.2326103471998804</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.05443528873695</v>
+        <v>0.03995741070208952</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.02852174733818636</v>
+        <v>-0.1306201600286002</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.031199259148524</v>
+        <v>0.01214593604561963</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.0001097780360444254</v>
+        <v>0.06191186696345127</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.04271997747001832</v>
+        <v>-0.2932399291245211</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.1530176983228995</v>
+        <v>0.494696055757268</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.1710306007460461</v>
+        <v>0.08729105115638473</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02592742460701501</v>
+        <v>-0.2779072491037159</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.04601244094351819</v>
+        <v>0.09066321500437352</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1171980830088324</v>
+        <v>0.4367377485024389</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0297444578947847</v>
+        <v>-0.001179578107944693</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.07218701529404269</v>
+        <v>-0.2980220990121947</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4437,13 +4437,13 @@
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07955722477035301</v>
+        <v>0.4263673261334855</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.01989387177700752</v>
+        <v>-0.1472159722774553</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.07658656846726218</v>
+        <v>-0.3112491614714996</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0</v>
@@ -4467,52 +4467,52 @@
         <v>-0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0232554849975025</v>
+        <v>-0.04738894910102438</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.03011694619659885</v>
+        <v>-0.116363636614799</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.006130274037043379</v>
+        <v>-0.1718166321315268</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0325563093212532</v>
+        <v>0.1852856953249746</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01266525733516611</v>
+        <v>-0.09086158833424937</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.02077944962607515</v>
+        <v>0.03687943960392574</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4524,19 +4524,19 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01811675906640363</v>
+        <v>0.1531031360942658</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.004595640256337432</v>
+        <v>0.001307835361972858</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.05424330911602684</v>
+        <v>-0.1781110829985861</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,37 +4548,37 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1427743884738514</v>
+        <v>0.8212130923712024</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.0241860027257284</v>
+        <v>-0.2713493471161611</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1190901994750577</v>
+        <v>-0.3996711777458873</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.05095278649583195</v>
+        <v>0.09906814300631124</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,16 +4587,16 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.04178297285953764</v>
+        <v>-0.001699221152777965</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.02863651727521329</v>
+        <v>-0.170573968053862</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>-0</v>
@@ -4605,22 +4605,22 @@
         <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0400988153739593</v>
+        <v>0.09776080929121898</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.02296878605323514</v>
+        <v>0.1261035976057896</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01809499799174784</v>
+        <v>0.1260722373630456</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
@@ -4629,10 +4629,10 @@
         <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.06685476278099992</v>
+        <v>0.3320378188517385</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.007589476822782236</v>
+        <v>-0.1199320038765693</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.04119877442006527</v>
+        <v>-0.3479481021728571</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4656,10 +4656,10 @@
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.03665777265738648</v>
+        <v>-0.2778191770766232</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
@@ -4668,10 +4668,10 @@
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001474131626043238</v>
+        <v>-0.03500939406261717</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03607564203071573</v>
+        <v>0.2183310126639291</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
@@ -4680,52 +4680,52 @@
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.008135646229607902</v>
+        <v>-0.2517274813914074</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.001622213342231009</v>
+        <v>0.0510324848002276</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.008023215206844221</v>
+        <v>0.1169712303859978</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.02965289993634218</v>
+        <v>-0.259437009078495</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.002328942415486387</v>
+        <v>-0.02332465346922123</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04239141731259345</v>
+        <v>0.2002404733138211</v>
       </c>
       <c r="DB8" t="n">
         <v>-0</v>
@@ -4734,25 +4734,25 @@
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.0295546070805341</v>
+        <v>-0.09889313755934424</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05793182114216402</v>
+        <v>-0.149345908973724</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01216507295986208</v>
+        <v>0.1989045246279575</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,31 +4761,31 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.008160263771279347</v>
+        <v>-0.07024722566447676</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.02536545656138136</v>
+        <v>-0.02954082494299254</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.01545211013315832</v>
+        <v>0.0804138591930242</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>-0</v>
@@ -4794,19 +4794,19 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.03496817045983919</v>
+        <v>0.1673940841061969</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01946406319432611</v>
+        <v>0.02918889793659517</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.01054990128741557</v>
+        <v>0.06311126499794864</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4815,13 +4815,13 @@
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.02587885789065273</v>
+        <v>-0.1186869445558035</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
@@ -4830,64 +4830,64 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.009079924635044211</v>
+        <v>-0.07371437560346461</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.02448550222091561</v>
+        <v>0.2057695472875113</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.01890787144316965</v>
+        <v>-0.1748834559410222</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.002878079052189427</v>
+        <v>-0.1366501138729635</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01848538777164039</v>
+        <v>0.1606327195617072</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03119435134340029</v>
+        <v>-0.2773612074681751</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.005355355349752282</v>
+        <v>-0.08030608432345285</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03978652583145841</v>
+        <v>0.2069456970913051</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
@@ -4896,40 +4896,40 @@
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02105964150855761</v>
+        <v>-0.1696388861132056</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.02894591541153857</v>
+        <v>0.06726298848662383</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03742582556853335</v>
+        <v>0.2197978643127874</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.03004516117535081</v>
+        <v>-0.05813431737098057</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,90 +4938,90 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.01013922765638659</v>
+        <v>0.05770671171993089</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.002247322903840277</v>
+        <v>0.02889470530433905</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02723309730920663</v>
+        <v>-0.1123726325956484</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.02326882643855663</v>
+        <v>0.1379702473586978</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3409480458315611</v>
+        <v>0.514634084820257</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0882610255695918</v>
+        <v>-0.2126914909904479</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05332677924094302</v>
+        <v>-0.1354820559105151</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2174472420448091</v>
+        <v>0.4292121398422543</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0844096120392112</v>
+        <v>-0.3332839980488304</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.07265916701045778</v>
+        <v>-0.1879167258018003</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5030,28 +5030,28 @@
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1079261319799305</v>
+        <v>0.1717885457520988</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.02333603929325449</v>
+        <v>0.03180388619914749</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.007792937736053018</v>
+        <v>-0.08611416499864701</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
@@ -5063,100 +5063,100 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.06848515022276307</v>
+        <v>0.03960292571250731</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02797625986687783</v>
+        <v>-0.1190691648637011</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.05381509366668981</v>
+        <v>-0.09901473063382051</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.05384672924153084</v>
+        <v>0.2591433450829718</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.04615413956379726</v>
+        <v>0.01568923282939872</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.05950491103559631</v>
+        <v>0.1004153133339139</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4818470150693195</v>
+        <v>0.6256642696697438</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.07335205842478577</v>
+        <v>-0.2939574327274639</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1126121514888296</v>
+        <v>-0.3641349645525648</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.04677682121986485</v>
+        <v>0.03233885215045519</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.05411724840583087</v>
+        <v>-0.1166747667582229</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1616767108145166</v>
+        <v>-0.02743261261966013</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.08577441667768332</v>
+        <v>-0.03136336831896519</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.07374509511599217</v>
+        <v>0.08172858133464828</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1030871039022891</v>
+        <v>0.1590196771370651</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,43 +5201,43 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2229764694880325</v>
+        <v>0.4364283139635423</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.01835447695473421</v>
+        <v>-0.2032698401065811</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.01942707977064607</v>
+        <v>-0.08618873110923146</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.09659078520116234</v>
+        <v>-0.2257331767473102</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.03595580494334936</v>
+        <v>0.2296819546325227</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01697471519213165</v>
+        <v>0.02780297624900161</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
@@ -5249,25 +5249,25 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.0124308326996939</v>
+        <v>-0.1314009204953563</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.01425300433081923</v>
+        <v>0.02454464863068305</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.05822263477704647</v>
+        <v>0.01084778475748236</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,22 +5276,22 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.09004426073766549</v>
+        <v>-0.2396056968055497</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.06255687788727442</v>
+        <v>0.2349124709320994</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.01960862100546691</v>
+        <v>0.03806658445966665</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5303,28 +5303,28 @@
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.06644288015820107</v>
+        <v>-0.1970702621236829</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1571715705597835</v>
+        <v>0.1755543027130478</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.01451085596167069</v>
+        <v>-0.06333737147374621</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,22 +5336,22 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.06330218913384823</v>
+        <v>-0.1586513060288081</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.05380705433835892</v>
+        <v>0.12105059871481</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01888713161856597</v>
+        <v>-0.1208612380516477</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,52 +5363,52 @@
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.03565440865252879</v>
+        <v>0.08248604240932385</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.01017202864849013</v>
+        <v>0.1531958336427601</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.02416829597382869</v>
+        <v>-0.1040842808949041</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.07486213147535699</v>
+        <v>-0.1389541167127458</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0.09193752271649862</v>
+        <v>-0.2929504983104569</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0636174140027433</v>
+        <v>0.04179703983551403</v>
       </c>
       <c r="EK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.07906170015211055</v>
+        <v>-0.1925835882808054</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0880770254519907</v>
+        <v>0.1319637588831103</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.05656002812457805</v>
+        <v>-0.04008322596275894</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5441,19 +5441,19 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.08787895133660073</v>
+        <v>-0.2658281990290166</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.06025911007907151</v>
+        <v>0.2435166674968536</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.02485929918810348</v>
+        <v>0.01721498596465412</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
@@ -5465,25 +5465,25 @@
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.01253256014250488</v>
+        <v>-0.05243663873089501</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04044675028645455</v>
+        <v>-0.06995039804038099</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.01824303345857761</v>
+        <v>0.06784038443621908</v>
       </c>
       <c r="FL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM9" t="n">
         <v>-0</v>
@@ -5492,22 +5492,22 @@
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.004291565025621778</v>
+        <v>-0.1372615463547336</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.01191723599327498</v>
+        <v>0.3829849399052879</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.0650916329030328</v>
+        <v>0.1294747878509005</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
@@ -5522,28 +5522,28 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02410194614712993</v>
+        <v>-0.1921508906539649</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.03421951383415536</v>
+        <v>0.1040371064804531</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
@@ -5551,133 +5551,133 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.05308925157294307</v>
+        <v>-0.1322002581316939</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1620083909077807</v>
+        <v>0.07605184891905219</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.126087700757997</v>
+        <v>-0.0294562318558092</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.03016205663653722</v>
+        <v>-0.01294667954477114</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.003154124324299802</v>
+        <v>-0.1258068196351121</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08789134874590183</v>
+        <v>0.03821584249282375</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04921741822226476</v>
+        <v>-0.08342617427030398</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.02787241510516185</v>
+        <v>-0.03808615116977025</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.03937066250317035</v>
+        <v>0.03853584616371496</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08443222566284914</v>
+        <v>-0.07311923133252889</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03957960040807695</v>
+        <v>-0.0553080523179293</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.05212808335839594</v>
+        <v>0.0105374723316995</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.02886248799196908</v>
+        <v>0.1551811224497283</v>
       </c>
       <c r="AC10" t="n">
         <v>-0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.04159648088369793</v>
+        <v>-0.1069274615895952</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.04372693457807797</v>
+        <v>-0.2339484879634397</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.008568053964858805</v>
+        <v>0.01613882335497175</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.008396173776619057</v>
+        <v>-0.03080460976441219</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.05320854317335374</v>
+        <v>-0.03653955038299216</v>
       </c>
       <c r="AN10" t="n">
         <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.006571484075759319</v>
+        <v>-0.1118143131403498</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.004038960139380969</v>
+        <v>0.06956553251639512</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5686,79 +5686,79 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.05847884569719096</v>
+        <v>-0.1526818426604385</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2230192006373052</v>
+        <v>0.0906741255408274</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3754557746575299</v>
+        <v>-0.2795019676916896</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.01293782563973349</v>
+        <v>0.05778424265300571</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.08532011008472291</v>
+        <v>-0.01868401774981726</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0002004662246627508</v>
+        <v>-0.07243810770920775</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.03836266574160838</v>
+        <v>0.15382856312485</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0.04112322371023727</v>
+        <v>-0.1229287948139233</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0.005912155802801428</v>
+        <v>0.02336681780832149</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.1251293264349907</v>
+        <v>0.0714753894968667</v>
       </c>
       <c r="BO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.03084126522261589</v>
+        <v>0.07087681085009659</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.02482131363140076</v>
+        <v>0.02979957788108645</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5767,25 +5767,25 @@
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0.02069883168775851</v>
+        <v>-0.02497798857237962</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.06091364954977534</v>
+        <v>0.04097132109504999</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.213662427372858</v>
+        <v>-0.06501859521106898</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0.02199217145805286</v>
+        <v>0.04031400367143013</v>
       </c>
       <c r="CB10" t="n">
         <v>-0</v>
@@ -5794,187 +5794,187 @@
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.03415831570398315</v>
+        <v>0.03440651058158465</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF10" t="n">
-        <v>-0.0513557438417854</v>
+        <v>0.03031574794419616</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.04180147166540532</v>
+        <v>0.06374765480122643</v>
       </c>
       <c r="CI10" t="n">
         <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.02381211492951983</v>
+        <v>0.03204170634168112</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.02383471039820621</v>
+        <v>-0.05463237026154361</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>-0.002836302715499468</v>
+        <v>0.04001918684012154</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.07358186747663276</v>
+        <v>-0.009179506449982812</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0.001236278279851694</v>
+        <v>0.01197844278755526</v>
       </c>
       <c r="CT10" t="n">
         <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.02033991801365712</v>
+        <v>0.05339788790731637</v>
       </c>
       <c r="CW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0.04644588459588962</v>
+        <v>-0.01257023956024611</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.01468683874765903</v>
+        <v>0.02034719418682673</v>
       </c>
       <c r="DA10" t="n">
         <v>-0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.02879710824739396</v>
+        <v>0.03358726979210025</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.02698858859057114</v>
+        <v>0.002487828407161779</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0.06641437481755723</v>
+        <v>-0.03891428511672262</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.03442527490009943</v>
+        <v>0.174889519216406</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.03046988445727654</v>
+        <v>-0.01383429880584694</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.05952294995032164</v>
+        <v>-0.09659343334676421</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.01599107091476255</v>
+        <v>0.01760523659593753</v>
       </c>
       <c r="DQ10" t="n">
         <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.0007819657321248059</v>
+        <v>-0.1787178189167618</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.04669034380016306</v>
+        <v>-0.04655501212890574</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.01729735978692709</v>
+        <v>0.144612302753559</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY10" t="n">
-        <v>-0.002411324416861088</v>
+        <v>0.01421052417507925</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.06181619662910364</v>
+        <v>-0.1018267353883325</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0.004799222326474946</v>
+        <v>-0.0008295135274328546</v>
       </c>
       <c r="ED10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0005971680886504736</v>
+        <v>0.003375930729164833</v>
       </c>
       <c r="EG10" t="n">
         <v>0</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0.1204862516825976</v>
+        <v>0.005759714443908848</v>
       </c>
       <c r="EI10" t="n">
         <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.008493161757983474</v>
+        <v>0.01786774345982451</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0.0004621125432764574</v>
+        <v>0.1374615750957946</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,79 +5983,79 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0206005374854761</v>
+        <v>0.1791104100024897</v>
       </c>
       <c r="EP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0.02605980590032429</v>
+        <v>0.06847223546999966</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.08876062446305764</v>
+        <v>0.01168059176086653</v>
       </c>
       <c r="ET10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0.01518193813589657</v>
+        <v>0.1049013078273466</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.01831080207850771</v>
+        <v>0.03947510841700585</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ10" t="n">
-        <v>-0.04650112384177072</v>
+        <v>-0.01459710574364585</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.03339351545933894</v>
+        <v>0.04279788657955287</v>
       </c>
       <c r="FC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.02360781147461712</v>
+        <v>0.01839546422814685</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.02008166584856643</v>
+        <v>0.2522585820987032</v>
       </c>
       <c r="FH10" t="n">
         <v>-0</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0.02482219312856452</v>
+        <v>-0.04630851468112528</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.004291173595744819</v>
+        <v>0.1317433648082941</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0.03304331805289434</v>
+        <v>0.05469969901190738</v>
       </c>
       <c r="FN10" t="n">
         <v>0</v>
@@ -6064,40 +6064,40 @@
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.03780982346866996</v>
+        <v>0.224641637069548</v>
       </c>
       <c r="FQ10" t="n">
         <v>0</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.05753104081117454</v>
+        <v>-0.1664846046263572</v>
       </c>
       <c r="FS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.06437869347173751</v>
+        <v>0.06866294442332958</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.004537221142653486</v>
+        <v>0.003837574711007139</v>
       </c>
       <c r="FW10" t="n">
         <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0.01765752031578536</v>
+        <v>0.0804791813625528</v>
       </c>
       <c r="FZ10" t="n">
         <v>-0</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.04370553028855286</v>
+        <v>0.008649437890740554</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
@@ -6106,39 +6106,39 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0.02584325399821205</v>
+        <v>0.01743789980609147</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1222571020837711</v>
+        <v>0.686059409134513</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02229399850385637</v>
+        <v>0.01083809512969205</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07343490555949657</v>
+        <v>-0.336035525314876</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09341916439165535</v>
+        <v>0.7367211740592864</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,70 +6159,70 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01390163377877261</v>
+        <v>-0.1688405861707961</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.05565770108542291</v>
+        <v>-0.2844688922844916</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01528906237972979</v>
+        <v>0.1395593015930978</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01817242975627942</v>
+        <v>-0.1011703392351819</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01214445645639084</v>
+        <v>-0.1006298242747681</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02597622746630741</v>
+        <v>0.106817413328804</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0180747886140635</v>
+        <v>-0.2569007513532548</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01421087544218243</v>
+        <v>-0.04638501513691631</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.01596118049372201</v>
+        <v>0.2345043416093439</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.007111805229606546</v>
+        <v>0.03719604704706854</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.04338272611644452</v>
+        <v>-0.2198871199890317</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1141507754450967</v>
+        <v>1.091197145535905</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
@@ -6267,10 +6267,10 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.002018597276012327</v>
+        <v>-0.3726887698222477</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.07380442145166065</v>
+        <v>-0.3206878056024413</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -6279,13 +6279,13 @@
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.05886930634372867</v>
+        <v>-0.04386949278700885</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,52 +6294,52 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.0429769922863655</v>
+        <v>-0.09077410646586173</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.03436294012080677</v>
+        <v>-0.2012657041847653</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>-0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.03547951499602282</v>
+        <v>0.1646048898928631</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01496302973413878</v>
+        <v>0.1567977482755831</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.007548467433364106</v>
+        <v>0.06300869395101974</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.04980387575145992</v>
+        <v>0.5929616845664558</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,13 +6348,13 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.002803267555271939</v>
+        <v>-0.08572751412602862</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.03242125014868476</v>
+        <v>-0.273009072530041</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
         <v>-0</v>
@@ -6363,25 +6363,25 @@
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.02942346177446641</v>
+        <v>-0.3262361961648461</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.0003924665936483321</v>
+        <v>0.02724794870148863</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02303259001860206</v>
+        <v>0.2064169371416778</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,22 +6393,22 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.007706241185761316</v>
+        <v>-0.2553031541795094</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0004566390945135816</v>
+        <v>0.1471557545475157</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.009121556966216925</v>
+        <v>0.1190204245949742</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
         <v>0</v>
@@ -6420,22 +6420,22 @@
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02528512653948935</v>
+        <v>-0.3098630954751745</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.001939171490754589</v>
+        <v>-0.007036311899689467</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02667439877548705</v>
+        <v>0.1948843593636193</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6447,19 +6447,19 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.00676445036870865</v>
+        <v>-0.05153725611312894</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01285384942011224</v>
+        <v>-0.1090564694271219</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02097151283361084</v>
+        <v>0.08143251050659105</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,25 +6468,25 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.006990855926376112</v>
+        <v>-0.1385534847191706</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.03202506901246444</v>
+        <v>-0.04369755286124345</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.002017596732566559</v>
+        <v>0.1339733484630864</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
@@ -6501,46 +6501,46 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.02829706534901172</v>
+        <v>0.03941265658156573</v>
       </c>
       <c r="DY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ11" t="n">
         <v>0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.02430809855248036</v>
+        <v>-0.0224059710694349</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.002094011577464539</v>
+        <v>-0.04524683087418831</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.02265537367026065</v>
+        <v>-0.1007080089071653</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.004807634338902141</v>
+        <v>-0.1266381002673199</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0104341564334787</v>
+        <v>0.1190126443851689</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6549,82 +6549,82 @@
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.02274771518049499</v>
+        <v>-0.2344207344158795</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.01774955469326118</v>
+        <v>-0.07575750363527867</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.02122474363395636</v>
+        <v>0.06988808497737188</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02773420579493395</v>
+        <v>-0.3403990325391515</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.003466357239189167</v>
+        <v>-0.03268879719468643</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02756139570939054</v>
+        <v>0.1814403237911446</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.008454145435599816</v>
+        <v>-0.2960221800188088</v>
       </c>
       <c r="FI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02968629913561758</v>
+        <v>0.1094746896849649</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03087649153255465</v>
+        <v>0.2070170732961777</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
         <v>0</v>
@@ -6633,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01280051331709561</v>
+        <v>-0.1512398403390641</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,43 +6645,43 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.004822268711872176</v>
+        <v>0.05843207306767936</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.0009922761293481095</v>
+        <v>-0.005082808823363241</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.02242614867186905</v>
+        <v>-0.1362168743144561</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.02566725205355864</v>
+        <v>0.009449116646352149</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,19 +6692,19 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4581457999169908</v>
+        <v>0.3423687194099963</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.195251768947324</v>
+        <v>-0.3764095297401692</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1405952929958347</v>
+        <v>0.02096703592921727</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6713,22 +6713,22 @@
         <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3911622091551109</v>
+        <v>0.3566630988989717</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1455852409836318</v>
+        <v>-0.3590745214046546</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1585724936682986</v>
+        <v>0.01053370267458974</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6746,19 +6746,19 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1045965849858729</v>
+        <v>0.09575490586536266</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.0007820459508892608</v>
+        <v>-0.03119925043474921</v>
       </c>
       <c r="W12" t="n">
-        <v>0.113499990330146</v>
+        <v>-0.2226054221053229</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6767,28 +6767,28 @@
         <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2031190590959953</v>
+        <v>0.0005864035618474978</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.002975104570467792</v>
+        <v>-0.141471784312988</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02467575569419562</v>
+        <v>-0.1357002709336085</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,46 +6797,46 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.009034442387666262</v>
+        <v>0.1861533232524599</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.06239806982659429</v>
+        <v>-0.07841230284084456</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.111579365371324</v>
+        <v>0.02571024823129385</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5639674297932005</v>
+        <v>0.4158628454104595</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.0677351330334873</v>
+        <v>-0.1629862670574193</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.01254793514577317</v>
+        <v>-0.3598606582503024</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6851,19 +6851,19 @@
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1076582928969678</v>
+        <v>-0.07835138688065764</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.07984750389615544</v>
+        <v>-0.1067382552304633</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.08577684755992197</v>
+        <v>-0.04773469499311157</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6878,19 +6878,19 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.143270008980353</v>
+        <v>0.0164191971338173</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.04741458861699344</v>
+        <v>0.1071129158894381</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1945729962862967</v>
+        <v>0.08350413276237371</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2889044222431492</v>
+        <v>0.2763360695821286</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.02238646590037053</v>
+        <v>-0.1479338387410397</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.07755096706003113</v>
+        <v>-0.08150101128979159</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1128265711340619</v>
+        <v>-0.1732648251671587</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.02749979241129626</v>
+        <v>0.2430731106853436</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.02612296057896357</v>
+        <v>0.0308464935359105</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,52 +6962,52 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.09090737559423483</v>
+        <v>-0.0362554152229585</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.07602186507200255</v>
+        <v>0.4521541104264092</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.113845487949422</v>
+        <v>0.1233125928576393</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.09999111531999121</v>
+        <v>-0.1508777985624592</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.04456363815421914</v>
+        <v>0.2554936114357929</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0147805045977858</v>
+        <v>0.03288525161917675</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,43 +7016,43 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-9.59514030766385e-05</v>
+        <v>0.01888038760959661</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.152733070186265</v>
+        <v>0.09353441537321062</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01166241104097987</v>
+        <v>-0.04199229272691154</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.1032359226430624</v>
+        <v>-0.1685729981094011</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.09128230117340425</v>
+        <v>0.1896255748466748</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.09882602061455634</v>
+        <v>0.01316789440209192</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
@@ -7064,22 +7064,22 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.1557333589749884</v>
+        <v>-0.1112364315696641</v>
       </c>
       <c r="DY12" t="n">
         <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.03497940716414107</v>
+        <v>-0.1412214277830183</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.09300351403559889</v>
+        <v>-0.1951573939355091</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
@@ -7088,34 +7088,34 @@
         <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.1004609855501708</v>
+        <v>-0.05589273586137254</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.1040595637848238</v>
+        <v>0.1626194759473193</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.1643389853047998</v>
+        <v>0.06139219683850177</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,25 +7124,25 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.0895873070853568</v>
+        <v>-0.1477381038288452</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03263581677445042</v>
+        <v>0.1550039092138548</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.08105306434459819</v>
+        <v>-0.03310901480676269</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,16 +7151,16 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.09870603868216123</v>
+        <v>-0.1731965825756248</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.04724306841194674</v>
+        <v>0.2654501726218733</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.04354021502619825</v>
+        <v>0.008623979263121726</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,25 +7169,25 @@
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.1546097896382724</v>
+        <v>-0.09664059741758441</v>
       </c>
       <c r="FI12" t="n">
         <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.05735982576347428</v>
+        <v>0.1052552939535814</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.09247609876329156</v>
+        <v>-0.2243478053870123</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,7 +7196,7 @@
         <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
@@ -7205,16 +7205,16 @@
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0272053815419953</v>
+        <v>-0.02663036973649215</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.03026647874411024</v>
+        <v>-0.03927093881445466</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.07379229753290598</v>
+        <v>0.08383904285287939</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
@@ -7229,16 +7229,16 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.06820140594287177</v>
+        <v>-0.1011707693394835</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.04736260767577824</v>
+        <v>0.2592877304777086</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
@@ -7247,18 +7247,18 @@
         <v>-0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1832546879879849</v>
+        <v>0.1313949587382843</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -7267,25 +7267,25 @@
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1301779039673419</v>
+        <v>-0.2379177339093157</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1001323620442995</v>
+        <v>0.08335055613922747</v>
       </c>
       <c r="F13" t="n">
         <v>-0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1818314061866161</v>
+        <v>0.07876739082942742</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -7294,25 +7294,25 @@
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.04280223886547486</v>
+        <v>-0.2948321791257638</v>
       </c>
       <c r="N13" t="n">
-        <v>0.04753530098885444</v>
+        <v>0.0281168775846353</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03385071337707975</v>
+        <v>-0.02190189311320534</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -7321,40 +7321,40 @@
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.08430672962715172</v>
+        <v>-0.05443974083825935</v>
       </c>
       <c r="W13" t="n">
-        <v>0.05423348448006593</v>
+        <v>-0.06259513992160202</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.04582488326946066</v>
+        <v>0.04198593758607697</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.03738802576913945</v>
+        <v>0.05853972744482955</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.007246504202829296</v>
+        <v>0.1967519671284427</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -7363,49 +7363,49 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.0185761018253925</v>
+        <v>0.03702178347942817</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.01623220645261452</v>
+        <v>-0.1529305940886349</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.05829110836056694</v>
+        <v>0.05627732162524565</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.1244984537409706</v>
+        <v>-0.0952951731480968</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.07346661816571966</v>
+        <v>-0.3565859525642641</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1811601101822725</v>
+        <v>-0.02216417264625447</v>
       </c>
       <c r="AY13" t="n">
         <v>-0</v>
@@ -7420,7 +7420,7 @@
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.1568638780500055</v>
+        <v>0.1954027748129445</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -7429,37 +7429,37 @@
         <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.004395966709541831</v>
+        <v>0.2299432740768372</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.05403257386471631</v>
+        <v>0.175459910016169</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.07036153631456421</v>
+        <v>-0.004435995454128621</v>
       </c>
       <c r="BM13" t="n">
         <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.01815935185884582</v>
+        <v>0.01592056012766048</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.121980376786556</v>
+        <v>-0.1040902684376998</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
@@ -7468,25 +7468,25 @@
         <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.05468390810137329</v>
+        <v>-0.064372198416355</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW13" t="n">
         <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0.001997394515624398</v>
+        <v>-0.2462635076806881</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.08779394210697841</v>
+        <v>-0.05006215238014487</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0.03375306575527092</v>
+        <v>-0.05579956628064316</v>
       </c>
       <c r="CE13" t="n">
         <v>0</v>
@@ -7510,16 +7510,16 @@
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.01691641108638595</v>
+        <v>0.1076455019221433</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.02948979913626301</v>
+        <v>-0.02159103826348807</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7528,46 +7528,46 @@
         <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-0.03789221890167208</v>
+        <v>-0.005023301647346065</v>
       </c>
       <c r="CN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.09060938956881297</v>
+        <v>0.1082979905411421</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.08786999162397291</v>
+        <v>-0.04375023605889042</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0.01923109314232521</v>
+        <v>-0.04822647152341256</v>
       </c>
       <c r="CW13" t="n">
         <v>-0</v>
       </c>
       <c r="CX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.002121917516081131</v>
+        <v>0.1097972934887758</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.01939521487907567</v>
+        <v>-0.006299821832123778</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
@@ -7582,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0.01622913812404454</v>
+        <v>-0.01728180564368446</v>
       </c>
       <c r="DF13" t="n">
         <v>-0</v>
@@ -7591,10 +7591,10 @@
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.08024442334720126</v>
+        <v>0.125608845464848</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.03083544699488713</v>
+        <v>-0.01718535980070633</v>
       </c>
       <c r="DJ13" t="n">
         <v>0</v>
@@ -7609,7 +7609,7 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0.03332696488965708</v>
+        <v>-0.07858278232786911</v>
       </c>
       <c r="DO13" t="n">
         <v>-0</v>
@@ -7618,70 +7618,70 @@
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.05631059640296467</v>
+        <v>0.01375399013548524</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.08116549735136346</v>
+        <v>0.009090790552844964</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0.04959929932461602</v>
+        <v>0.009161861048117458</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.02227968461882477</v>
+        <v>0.01187137089506876</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.04930752316829347</v>
+        <v>0.02758356649850295</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0.02988942689649849</v>
+        <v>-0.0859969553425079</v>
       </c>
       <c r="EG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.02156817887165146</v>
+        <v>0.08604183199908295</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.009019646908212404</v>
+        <v>0.02611959091290924</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>0</v>
@@ -7690,46 +7690,46 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.001073827891032636</v>
+        <v>0.04130366432474115</v>
       </c>
       <c r="EP13" t="n">
         <v>0</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.02348733396979597</v>
+        <v>0.1295864379985639</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01562763953774191</v>
+        <v>0.00465093059836375</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0.02197499510018477</v>
+        <v>-0.05323207404291099</v>
       </c>
       <c r="EY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.01000476851334429</v>
+        <v>0.1444271555153186</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.03033385643913468</v>
+        <v>-0.01190029685814525</v>
       </c>
       <c r="FC13" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0.02340801250640178</v>
+        <v>0.01591307790194845</v>
       </c>
       <c r="FH13" t="n">
         <v>0</v>
@@ -7753,10 +7753,10 @@
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0309616760866224</v>
+        <v>0.1099043697582282</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.1433913500694</v>
+        <v>0.1329852356407022</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
@@ -7765,49 +7765,49 @@
         <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
         <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.006455184193783856</v>
+        <v>-0.005566299121230172</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
       </c>
       <c r="FS13" t="n">
-        <v>-0.008536268434706657</v>
+        <v>0.2229713303526088</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.06151449591621223</v>
+        <v>0.07192957817993348</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.02812878885834055</v>
+        <v>0.02216242221761032</v>
       </c>
       <c r="FZ13" t="n">
         <v>0</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.03002682733847973</v>
+        <v>0.1955895620366948</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
@@ -8968,25 +8968,25 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.5410650417302539</v>
+        <v>0.2660736399776018</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2186956843750731</v>
+        <v>-0.2085204482765376</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04234275110369674</v>
+        <v>-0.04162360649000274</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8995,22 +8995,22 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3391264047132533</v>
+        <v>0.2719698924398298</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2575222694645799</v>
+        <v>-0.2848511115016212</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.05105648135955424</v>
+        <v>-0.1213750727437638</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9022,76 +9022,76 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1129925529529755</v>
+        <v>0.03823933318164493</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.00346506180548008</v>
+        <v>-0.0631894605137595</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1688062280249126</v>
+        <v>-0.08779508458910966</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.09525192370182696</v>
+        <v>-0.07082034053217726</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.03305362443468953</v>
+        <v>-0.1117693709136719</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.05509657271721064</v>
+        <v>-0.104725088643386</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.01442002826773686</v>
+        <v>0.1038450597638386</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.06262277521612936</v>
+        <v>-0.1161764373941385</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.008456635264774368</v>
+        <v>0.03506535318098086</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9103,25 +9103,25 @@
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.4724017186805892</v>
+        <v>0.2435336264475849</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.08854572750913811</v>
+        <v>-0.06789555347647135</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.165601607781852</v>
+        <v>-0.2365325110729317</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,25 +9130,25 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.07474852195072852</v>
+        <v>-0.004874237614379486</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.250013619645823</v>
+        <v>-0.03829974173921458</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1741988633874698</v>
+        <v>-0.02714703093908335</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
@@ -9157,16 +9157,16 @@
         <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.1125216097528173</v>
+        <v>0.01387973704761446</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0.002906200494494469</v>
+        <v>0.07543688649984426</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1966445474554451</v>
+        <v>0.04221416144544397</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
@@ -9178,79 +9178,79 @@
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.170419104852483</v>
+        <v>0.1502481464754426</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.04513429900968592</v>
+        <v>-0.1298152267948166</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.1134842238350634</v>
+        <v>-0.05504992729178303</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.1167081432295917</v>
+        <v>-0.08063592152023971</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>-0.001629123506064846</v>
+        <v>0.1178810775852645</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.01660842357037158</v>
+        <v>0.02258076349303474</v>
       </c>
       <c r="CI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.01016528000915272</v>
+        <v>-0.04014350819245935</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.1929670511239723</v>
+        <v>0.1919890861146535</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.08914873335318979</v>
+        <v>0.07605351272939975</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9265,16 +9265,16 @@
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.08415097769637617</v>
+        <v>-0.07915744721034615</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.03383625292940547</v>
+        <v>0.1257474803176357</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.02892215135274137</v>
+        <v>0.03417689504331984</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
@@ -9283,25 +9283,25 @@
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.03301493313441553</v>
+        <v>-0.04596710580125536</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.06613367979840862</v>
+        <v>0.04010761922732572</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04972171076839693</v>
+        <v>-0.1021505892695015</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9316,22 +9316,22 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.06690917383507526</v>
+        <v>-0.06509309210597244</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0.01076686615457798</v>
+        <v>-0.04575952174076585</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.04579077897970114</v>
+        <v>0.01464978895847046</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9346,43 +9346,43 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.05142032546962331</v>
+        <v>0.004557727335303751</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0.04189487527347956</v>
+        <v>0.07307911212906019</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.0620150738588393</v>
+        <v>-0.03684014879745422</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.09905181271966418</v>
+        <v>-0.044100038398626</v>
       </c>
       <c r="EH16" t="n">
         <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>-0.01693174871910948</v>
+        <v>0.07615564029088313</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.08446259331482353</v>
+        <v>0.06184568354408385</v>
       </c>
       <c r="EK16" t="n">
         <v>0</v>
@@ -9394,22 +9394,22 @@
         <v>0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.007479309038581499</v>
+        <v>-0.003919785091076704</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.01879977261132918</v>
+        <v>0.08830448574057724</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.01925188711466313</v>
+        <v>-0.0367567581252814</v>
       </c>
       <c r="ET16" t="n">
         <v>0</v>
@@ -9427,43 +9427,43 @@
         <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.08216187635802955</v>
+        <v>-0.08397304739450392</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>-0.01538374525501239</v>
+        <v>0.1480380986391776</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.0002558869224159738</v>
+        <v>0.01086389039822438</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.006830584562478975</v>
+        <v>0.1118982525195784</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.001845107333583864</v>
+        <v>0.09308795794626157</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.00323249987371643</v>
+        <v>-0.01546683201624969</v>
       </c>
       <c r="FL16" t="n">
         <v>-0</v>
@@ -9475,55 +9475,55 @@
         <v>-0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.03958080542748853</v>
+        <v>0.03132247259518345</v>
       </c>
       <c r="FR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.03014346244889226</v>
+        <v>0.1337320026844632</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.04798300797478162</v>
+        <v>-0.02676272913338137</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.05636252763346204</v>
+        <v>-0.0003666280093737</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.1298154466729884</v>
+        <v>0.05651553371040832</v>
       </c>
       <c r="GC16" t="n">
         <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
         <v>0</v>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1720852308433508</v>
+        <v>0.2807783997243405</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,25 +9546,25 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0631298163844565</v>
+        <v>-0.02098773771440667</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.09825070727924362</v>
+        <v>-0.1374041107818829</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1399471843099789</v>
+        <v>0.3061053241222141</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9573,67 +9573,67 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.04594607403173458</v>
+        <v>-0.09742407102853537</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.08712877396884856</v>
+        <v>-0.1680275284495954</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01483910315556653</v>
+        <v>0.07053815477403315</v>
       </c>
       <c r="U17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.006137490590716664</v>
+        <v>-0.08500231874735353</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01462386789307619</v>
+        <v>-0.01588380446165712</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.008941371819549503</v>
+        <v>-0.03313477704535544</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01938489087789193</v>
+        <v>-0.1824732683994504</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.007619902547423086</v>
+        <v>0.03361802255592481</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
@@ -9645,22 +9645,22 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01083817071202681</v>
+        <v>0.02401003452150061</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01461398644290357</v>
+        <v>-0.03880435271243574</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.0140109319437402</v>
+        <v>0.004413489938820989</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,10 +9669,10 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1237250903075641</v>
+        <v>0.2575996401490129</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
@@ -9681,25 +9681,25 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.01775846022506024</v>
+        <v>-0.2324650735544868</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.02547568136752684</v>
+        <v>-0.09286135577308485</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
         <v>-0</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.04731951683753839</v>
+        <v>0.01170739138052894</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,52 +9708,52 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.06137849969626459</v>
+        <v>0.006344934629725137</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.07296465870638846</v>
+        <v>-0.06552645548157644</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.04499647216106174</v>
+        <v>0.0281083385639657</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.02364487689488501</v>
+        <v>0.06767752033155754</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.02385426936576697</v>
+        <v>-0.001649810406699377</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.05364093182359393</v>
+        <v>0.1286243121651954</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -9762,10 +9762,10 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.009449111495697292</v>
+        <v>-0.05767731136879675</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0.006448346036830239</v>
+        <v>-0.08515836651616135</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9774,40 +9774,40 @@
         <v>-0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.02973102005833553</v>
+        <v>-0.07451620285854098</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.003765786707016416</v>
+        <v>0.02403552083388472</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.02492895759825204</v>
+        <v>0.04945988437069602</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.008256125397190986</v>
+        <v>-0.04767662610100076</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,64 +9816,64 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.001361547467372726</v>
+        <v>0.1264869021897977</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.02379317154346143</v>
+        <v>0.07588341158631445</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.02257937450318364</v>
+        <v>-0.0771498251872956</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.005691992583672893</v>
+        <v>0.01884009051706865</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.02339790033916368</v>
+        <v>0.06744176617272457</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
         <v>-0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.01662272929147201</v>
+        <v>-0.01783010664187572</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.02566642577374316</v>
+        <v>-0.1034954369257002</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.01193417454267971</v>
+        <v>0.04923669257144197</v>
       </c>
       <c r="DK17" t="n">
         <v>-0</v>
@@ -9882,82 +9882,82 @@
         <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.007166953598033128</v>
+        <v>-0.002906864826687248</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01758145803396481</v>
+        <v>-0.06327346002413885</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.008533249537433929</v>
+        <v>0.04279317270654602</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.04143349024168581</v>
+        <v>0.01691423237676817</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.02085155628245685</v>
+        <v>-0.03422878067147822</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.01105089616490603</v>
+        <v>0.02569475330235464</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.03385460471301504</v>
+        <v>-0.03929122835377297</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
         <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.006443950724708173</v>
+        <v>0.02587811654052763</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.02200816244718907</v>
+        <v>0.001155649294275909</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
@@ -9966,82 +9966,82 @@
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.01051061435016654</v>
+        <v>-0.006602909192046962</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.004416208557531522</v>
+        <v>-0.007672299952023335</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.006849308551748133</v>
+        <v>0.08985366381717992</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.02370472817241398</v>
+        <v>-0.08640422430025997</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.009858920527999391</v>
+        <v>0.00435021010290157</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.02903936304480446</v>
+        <v>0.04041761031499658</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>-0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.02162679942715461</v>
+        <v>0.1660394017988398</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.007507920075557888</v>
+        <v>-0.07860580983848681</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01591432131001826</v>
+        <v>0.1065841754569732</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
@@ -10050,55 +10050,55 @@
         <v>0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.006465161574248761</v>
+        <v>0.06227246346236053</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.02164449336594215</v>
+        <v>-0.09309765963793083</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.01213124552035897</v>
+        <v>-0.02128411458872053</v>
       </c>
       <c r="FV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0008832941280612317</v>
+        <v>-0.03281324814190367</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.01187549525141698</v>
+        <v>0.06359948488301859</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10106,22 +10106,22 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5946216175763963</v>
+        <v>0.259537049322439</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.235764128396998</v>
+        <v>-0.2090480893715238</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08861121954490786</v>
+        <v>-0.02745702056920597</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
@@ -10133,16 +10133,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3896049083066717</v>
+        <v>0.2825937319569859</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2474286115817936</v>
+        <v>-0.2592767206043531</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.09300444890703999</v>
+        <v>-0.09298026786163803</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -10160,79 +10160,79 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1249194713127122</v>
+        <v>0.04480498817215502</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.02173451855532584</v>
+        <v>-0.05365545672531261</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1071754699592227</v>
+        <v>-0.06832299355758954</v>
       </c>
       <c r="X18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.04377955944807217</v>
+        <v>-0.06917978380024854</v>
       </c>
       <c r="AD18" t="n">
         <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.023695229886726</v>
+        <v>-0.1158428939391998</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.01053539446755433</v>
+        <v>-0.08575734923331436</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.02260603889746797</v>
+        <v>0.09175332054487594</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.06427696025924072</v>
+        <v>-0.09904326030676563</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.05707640080080482</v>
+        <v>0.03093875340763681</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -10241,25 +10241,25 @@
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.4971162910330704</v>
+        <v>0.231716991375388</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.03063124612559859</v>
+        <v>-0.07605620937571961</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.09650086539193224</v>
+        <v>-0.183911637143272</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>-0</v>
@@ -10268,25 +10268,25 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.05540753995728306</v>
+        <v>0.004096570886680441</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-0.2277858563944199</v>
+        <v>-0.06002395595403761</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.1416575720203862</v>
+        <v>-0.003055150320535974</v>
       </c>
       <c r="BH18" t="n">
         <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
         <v>0</v>
@@ -10295,19 +10295,19 @@
         <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.1568049848284083</v>
+        <v>0.009065607019788736</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.04638374390168714</v>
+        <v>0.06066883783248388</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.1816398240359392</v>
+        <v>0.05488164682488453</v>
       </c>
       <c r="BQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR18" t="n">
         <v>0</v>
@@ -10316,55 +10316,55 @@
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.1992698791415007</v>
+        <v>0.132298523972399</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.01022669180618649</v>
+        <v>-0.1068771885455356</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.06004513606653227</v>
+        <v>-0.02591230219297432</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
         <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.1110598510092496</v>
+        <v>-0.06829914799741937</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.009740860536533323</v>
+        <v>0.1048956195098666</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.01343252682830685</v>
+        <v>0.01395470270088745</v>
       </c>
       <c r="CI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -10376,25 +10376,25 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.01452133043728004</v>
+        <v>-0.05844166122804622</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>-0.1107069634946783</v>
+        <v>0.1624241157210889</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.0981823067352425</v>
+        <v>0.04413617197206595</v>
       </c>
       <c r="CR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS18" t="n">
         <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU18" t="n">
         <v>-0</v>
@@ -10403,16 +10403,16 @@
         <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.07622013518201778</v>
+        <v>-0.06727003904982144</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.04895921964307174</v>
+        <v>0.1082079747750656</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.02374720984801628</v>
+        <v>0.02649634810642618</v>
       </c>
       <c r="DA18" t="n">
         <v>0</v>
@@ -10424,22 +10424,22 @@
         <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.05709339663770158</v>
+        <v>-0.06794763434938006</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.06164073651377087</v>
+        <v>0.02558885980863026</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.03635273064433155</v>
+        <v>-0.02813545753154917</v>
       </c>
       <c r="DJ18" t="n">
         <v>-0</v>
@@ -10454,28 +10454,28 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.07576844449007651</v>
+        <v>-0.05691994172916</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0.009557070836316087</v>
+        <v>-0.02654710002775566</v>
       </c>
       <c r="DR18" t="n">
-        <v>-0.05952761921579852</v>
+        <v>0.002778315672388312</v>
       </c>
       <c r="DS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
         <v>0</v>
@@ -10484,16 +10484,16 @@
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.1093369534777668</v>
+        <v>0.01554953662174114</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0.01280035141197154</v>
+        <v>0.08018789140898699</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.05169659845450144</v>
+        <v>-0.05882786230714245</v>
       </c>
       <c r="EB18" t="n">
         <v>-0</v>
@@ -10505,55 +10505,55 @@
         <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.09095441669969091</v>
+        <v>-0.03789804458821881</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.01285261809264627</v>
+        <v>0.0701983689397688</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.06903194057714977</v>
+        <v>0.0569447427438711</v>
       </c>
       <c r="EK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.006454068171419602</v>
+        <v>-0.014148295062889</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.0007332371478921613</v>
+        <v>0.07301492772107196</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.03645330392819648</v>
+        <v>-0.03045352887986674</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
@@ -10565,22 +10565,22 @@
         <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.07607077715489657</v>
+        <v>-0.07230476975181285</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.006651942774291739</v>
+        <v>0.1300807097188973</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.01358052941290662</v>
+        <v>0.004046561043437618</v>
       </c>
       <c r="FC18" t="n">
         <v>-0</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
@@ -10592,16 +10592,16 @@
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.05670323286298735</v>
+        <v>0.1005023409315206</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>-0.000249341378067418</v>
+        <v>0.07404615228811703</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.0558769043104345</v>
+        <v>-0.04079984856910101</v>
       </c>
       <c r="FL18" t="n">
         <v>-0</v>
@@ -10613,28 +10613,28 @@
         <v>-0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.04972892123276148</v>
+        <v>0.04233961322989018</v>
       </c>
       <c r="FR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.0133055812899134</v>
+        <v>0.1435075782655539</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.07375949332678895</v>
+        <v>-0.04582746907336947</v>
       </c>
       <c r="FU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW18" t="n">
         <v>0</v>
@@ -10643,28 +10643,28 @@
         <v>0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.06805507426431964</v>
+        <v>-0.009515379181946103</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>-0.1229883396351646</v>
+        <v>0.04272269469237337</v>
       </c>
       <c r="GC18" t="n">
         <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG18" t="n">
         <v>-0</v>
@@ -10675,7 +10675,7 @@
         <v>-0</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.405238664604009</v>
+        <v>-0.136501467774088</v>
       </c>
       <c r="C19" t="n">
         <v>-0</v>
@@ -10684,13 +10684,13 @@
         <v>-0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03399917137986898</v>
+        <v>0.05298511329823975</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8716743515604034</v>
+        <v>0.2723918491103808</v>
       </c>
       <c r="G19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10699,10 +10699,10 @@
         <v>-0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3507129883318862</v>
+        <v>-0.1872272491659144</v>
       </c>
       <c r="L19" t="n">
         <v>-0</v>
@@ -10711,52 +10711,52 @@
         <v>-0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1220626223642566</v>
+        <v>0.08407630912268257</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6962474093679232</v>
+        <v>0.3444245620834467</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.04010564599849547</v>
+        <v>-0.06770333132832779</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V19" t="n">
         <v>-0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1590641607295891</v>
+        <v>0.05980121513002232</v>
       </c>
       <c r="X19" t="n">
-        <v>0.07878053277403445</v>
+        <v>0.05614491751718414</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>-0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.01142944619069088</v>
+        <v>0.02006631909336366</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -10765,10 +10765,10 @@
         <v>-0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.09938460414581955</v>
+        <v>0.06790000877917243</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.06951931288890462</v>
+        <v>-0.01446410015939961</v>
       </c>
       <c r="AH19" t="n">
         <v>-0</v>
@@ -10777,67 +10777,67 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK19" t="n">
         <v>-0</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.0541608506109875</v>
+        <v>-0.03575087846135901</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.008817895032192768</v>
+        <v>-0.003874876774620714</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.1493821532821759</v>
+        <v>0.0521714245479046</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>-0.2233531511821965</v>
+        <v>-0.2034340210724033</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW19" t="n">
         <v>-0</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.2342102365830175</v>
+        <v>0.03273391849286741</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.5478777386238182</v>
+        <v>0.160019986761322</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD19" t="n">
-        <v>-0.1858197089721497</v>
+        <v>0.1015587808703075</v>
       </c>
       <c r="BE19" t="n">
         <v>-0</v>
@@ -10846,64 +10846,64 @@
         <v>-0</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.02412405381198229</v>
+        <v>0.0504541294921671</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.1498430978741994</v>
+        <v>0.02526825528922824</v>
       </c>
       <c r="BI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ19" t="n">
         <v>0</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM19" t="n">
-        <v>-0.1920016215130404</v>
+        <v>-0.06043674056248306</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
       </c>
       <c r="BO19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>-0.09623603211103485</v>
+        <v>-0.04759125616954325</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.006045887353898303</v>
+        <v>-0.03784759569629495</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT19" t="n">
         <v>-0</v>
       </c>
       <c r="BU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV19" t="n">
-        <v>-0.1959903556245539</v>
+        <v>-0.13832994011035</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX19" t="n">
         <v>-0</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.07207165385800954</v>
+        <v>0.01069673731532533</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0.2673882247406092</v>
+        <v>0.1166868342995823</v>
       </c>
       <c r="CA19" t="n">
         <v>0</v>
@@ -10918,22 +10918,22 @@
         <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>0.09071355589533255</v>
+        <v>0.05121030501689779</v>
       </c>
       <c r="CF19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.008188332735688393</v>
+        <v>-0.03589696750820168</v>
       </c>
       <c r="CI19" t="n">
-        <v>-0.13628399609884</v>
+        <v>-0.0521475519483355</v>
       </c>
       <c r="CJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK19" t="n">
         <v>-0</v>
@@ -10945,25 +10945,25 @@
         <v>-0</v>
       </c>
       <c r="CN19" t="n">
-        <v>0.02104399278562502</v>
+        <v>0.03786793083774768</v>
       </c>
       <c r="CO19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.1528369562088899</v>
+        <v>-0.04283539392026337</v>
       </c>
       <c r="CR19" t="n">
-        <v>0.065722053267738</v>
+        <v>0.001263689887857653</v>
       </c>
       <c r="CS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU19" t="n">
         <v>0</v>
@@ -10972,7 +10972,7 @@
         <v>0</v>
       </c>
       <c r="CW19" t="n">
-        <v>0.06565903334639278</v>
+        <v>0.0470976421431121</v>
       </c>
       <c r="CX19" t="n">
         <v>-0</v>
@@ -10981,13 +10981,13 @@
         <v>-0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.01046144112433989</v>
+        <v>-0.04019658578803258</v>
       </c>
       <c r="DA19" t="n">
-        <v>-0.1373981029445382</v>
+        <v>-0.06850153175024556</v>
       </c>
       <c r="DB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC19" t="n">
         <v>0</v>
@@ -10996,37 +10996,37 @@
         <v>-0</v>
       </c>
       <c r="DE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.1238201279656669</v>
+        <v>0.08072287815156776</v>
       </c>
       <c r="DG19" t="n">
         <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.2196823853513855</v>
+        <v>0.05374305839566079</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.01083810037029535</v>
+        <v>-0.01287449269923724</v>
       </c>
       <c r="DK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL19" t="n">
         <v>-0</v>
       </c>
       <c r="DM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.02859263597070512</v>
+        <v>-0.03666184235524259</v>
       </c>
       <c r="DP19" t="n">
         <v>-0</v>
@@ -11035,13 +11035,13 @@
         <v>-0</v>
       </c>
       <c r="DR19" t="n">
-        <v>-0.02268784764219368</v>
+        <v>0.04112724804167377</v>
       </c>
       <c r="DS19" t="n">
-        <v>-0.03068275707062924</v>
+        <v>-0.06480916455454837</v>
       </c>
       <c r="DT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
@@ -11050,22 +11050,22 @@
         <v>0</v>
       </c>
       <c r="DW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>0.0956485681847447</v>
+        <v>0.07774372663285256</v>
       </c>
       <c r="DY19" t="n">
         <v>0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA19" t="n">
-        <v>-0.06929153921734954</v>
+        <v>0.023390151142781</v>
       </c>
       <c r="EB19" t="n">
-        <v>-0.1000274337961715</v>
+        <v>0.02543498305942117</v>
       </c>
       <c r="EC19" t="n">
         <v>0</v>
@@ -11074,28 +11074,28 @@
         <v>-0</v>
       </c>
       <c r="EE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF19" t="n">
         <v>-0</v>
       </c>
       <c r="EG19" t="n">
-        <v>0.05008556152196508</v>
+        <v>0.0415848194820586</v>
       </c>
       <c r="EH19" t="n">
         <v>0</v>
       </c>
       <c r="EI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>-0.02953957429850731</v>
+        <v>-0.03620023709002877</v>
       </c>
       <c r="EK19" t="n">
-        <v>-0.1173216582394399</v>
+        <v>-0.006424258465758396</v>
       </c>
       <c r="EL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM19" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
         <v>-0</v>
       </c>
       <c r="EP19" t="n">
-        <v>0.02799589060172723</v>
+        <v>0.03944065152066972</v>
       </c>
       <c r="EQ19" t="n">
         <v>0</v>
@@ -11116,40 +11116,40 @@
         <v>-0</v>
       </c>
       <c r="ES19" t="n">
-        <v>-0.02491263364668504</v>
+        <v>-0.04228905130337602</v>
       </c>
       <c r="ET19" t="n">
-        <v>-0.02294480499253993</v>
+        <v>0.04615898840423777</v>
       </c>
       <c r="EU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV19" t="n">
         <v>-0</v>
       </c>
       <c r="EW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX19" t="n">
         <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>0.05919634766393189</v>
+        <v>0.05637990358632906</v>
       </c>
       <c r="EZ19" t="n">
         <v>0</v>
       </c>
       <c r="FA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB19" t="n">
-        <v>-0.03467905339302266</v>
+        <v>-0.01548854930434335</v>
       </c>
       <c r="FC19" t="n">
-        <v>-0.1377331552007018</v>
+        <v>-0.06379144146929024</v>
       </c>
       <c r="FD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE19" t="n">
         <v>-0</v>
@@ -11161,19 +11161,19 @@
         <v>-0</v>
       </c>
       <c r="FH19" t="n">
-        <v>0.01000150452029809</v>
+        <v>-0.02638173424681817</v>
       </c>
       <c r="FI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ19" t="n">
         <v>0</v>
       </c>
       <c r="FK19" t="n">
-        <v>-0.007973888154101919</v>
+        <v>0.03247680503306904</v>
       </c>
       <c r="FL19" t="n">
-        <v>-0.1199009064387483</v>
+        <v>-0.07212226418641345</v>
       </c>
       <c r="FM19" t="n">
         <v>-0</v>
@@ -11188,52 +11188,52 @@
         <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>0.01640166191056296</v>
+        <v>0.01113706106233942</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT19" t="n">
-        <v>0.09870760767056674</v>
+        <v>0.09369398329108701</v>
       </c>
       <c r="FU19" t="n">
-        <v>-0.1234454368939907</v>
+        <v>0.08210149277252081</v>
       </c>
       <c r="FV19" t="n">
         <v>0</v>
       </c>
       <c r="FW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX19" t="n">
         <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>-0.05263942043303132</v>
+        <v>0.0581294240096003</v>
       </c>
       <c r="GA19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD19" t="n">
-        <v>0.0848534198827689</v>
+        <v>-0.03133289018972721</v>
       </c>
       <c r="GE19" t="n">
         <v>0</v>
       </c>
       <c r="GF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG19" t="n">
         <v>-0</v>
